--- a/INSTANCES/instances_xlsx/A_MTN_8/358FL_15A_2.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/358FL_15A_2.xlsx
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -11576,7 +11576,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -11610,7 +11610,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -11627,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -11644,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>1</v>
